--- a/output/pdf_financials_xlsx/GSI.xlsx
+++ b/output/pdf_financials_xlsx/GSI.xlsx
@@ -2266,13 +2266,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.116104</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.237796</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.165555</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.898331</v>
@@ -2287,22 +2287,22 @@
         <v>2.118812</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.029324</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.601034</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.604229</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.110859</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.72125</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>14.769751</v>
       </c>
     </row>
     <row r="35">
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.116104</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.237796</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.165555</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.898331</v>
@@ -2385,22 +2385,22 @@
         <v>2.118812</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.029324</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.601034</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.604229</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.110859</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>6.72125</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>14.769751</v>
       </c>
     </row>
     <row r="37">
@@ -2952,13 +2952,13 @@
         <v>2.38458</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.226258</v>
+        <v>0.110154</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.401556</v>
+        <v>0.16376</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.554862</v>
+        <v>0.389307</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.166325</v>
@@ -2973,22 +2973,22 @@
         <v>0.404318</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.990422</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.662918</v>
+        <v>0.061884</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.968631</v>
+        <v>0.364402</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.648316</v>
+        <v>0.537457</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.180675</v>
+        <v>0.459425</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.837459</v>
+        <v>1.067708</v>
       </c>
     </row>
     <row r="49">
@@ -6736,25 +6736,25 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019848</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.182979</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.1812</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.204372</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.232289</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.34726</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.378233</v>
       </c>
     </row>
     <row r="125">
@@ -6785,25 +6785,25 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019848</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.182979</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.1812</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.204372</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.232289</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.34726</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.378233</v>
       </c>
     </row>
     <row r="126">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -17292,7 +17292,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -25142,7 +25146,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -46400,7 +46408,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -46486,7 +46494,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSI.xlsx
+++ b/output/pdf_financials_xlsx/GSI.xlsx
@@ -2006,19 +2006,19 @@
         <v>0.362863</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.358564</v>
+        <v>0.000817</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.36511</v>
+        <v>0.000817</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.374866</v>
+        <v>0.000817</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.544779</v>
+        <v>0.000818</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.545843</v>
+        <v>0.000818</v>
       </c>
     </row>
     <row r="29">
@@ -2063,19 +2063,19 @@
         <v>2.471087</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.324663</v>
+        <v>-0.68241</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.808295</v>
+        <v>1.444002</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3.246288</v>
+        <v>2.872239</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>4.811041</v>
+        <v>4.26708</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.202947</v>
+        <v>-3.747972</v>
       </c>
     </row>
     <row r="30">
@@ -2120,19 +2120,19 @@
         <v>12.16291071881404</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1.884170928345756</v>
+        <v>-3.960343750943064</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>9.027352609577576</v>
+        <v>7.208732658628842</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.65681670452462</v>
+        <v>10.31367628336952</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>12.72393343548538</v>
+        <v>11.28530018428256</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-10.07685879199084</v>
+        <v>-11.79157338549015</v>
       </c>
     </row>
     <row r="31">
@@ -5566,19 +5566,19 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.000818</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.000818</v>
       </c>
     </row>
     <row r="101">
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.006673</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -15712,7 +15712,11 @@
           <t>Amortization – intangible asset</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -19494,7 +19498,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -20414,7 +20418,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -27926,7 +27934,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E247" s="5" t="n">
         <v>0.006673</v>
       </c>

--- a/output/pdf_financials_xlsx/GSI.xlsx
+++ b/output/pdf_financials_xlsx/GSI.xlsx
@@ -546,25 +546,17 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>5.152251</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3.839703</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4.040124</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>5.943773</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>9.899875</v>
@@ -603,25 +595,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>2.50503</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2.882018</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2.493737</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3.250899</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>4.848332</v>
@@ -660,25 +644,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>2.647221</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.957685</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.546387</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2.692874</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>5.051543</v>
@@ -717,25 +693,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -774,25 +742,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0.254801</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.495488</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.447885</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.635325</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.837369</v>
@@ -831,25 +791,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -888,25 +840,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>2.210581</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2.930544</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3.242825</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3.740182</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>4.243305</v>
@@ -945,25 +889,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-1.97286</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-1.696438</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-1.047308</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0.808238</v>
@@ -1002,25 +938,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1059,25 +987,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -1116,25 +1036,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -1173,25 +1085,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.023246</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.029187</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.125846</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -1230,25 +1134,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.131365</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.9207959999999999</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0.695566</v>
@@ -1287,25 +1183,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1314,10 +1202,10 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.030421</v>
+        <v>0.030421</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.030896</v>
+        <v>-0.030896</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-1.471</v>
@@ -1498,25 +1386,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.131365</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.9207959999999999</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0.695566</v>
@@ -1555,25 +1435,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1612,25 +1484,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1670,7 +1534,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-2.631462</v>
+        <v>0.131365</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-2.631462</v>
@@ -1728,15 +1592,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0.01</v>
@@ -1791,15 +1651,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0.01</v>
@@ -1854,15 +1710,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>33.30728</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46.0398</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1913,25 +1765,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.131365</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.9207959999999999</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.695566</v>
@@ -1970,25 +1814,17 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.051328</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.050101</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.04445</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2027,25 +1863,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.182693</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-2.581361</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-1.620914</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.9207959999999999</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.695566</v>
@@ -2084,25 +1912,17 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>3.545887030736662</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-67.22814238497092</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-40.1204022450796</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-15.49177601499922</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>7.026007904140203</v>
@@ -2141,25 +1961,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -2198,25 +2010,17 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>2.549662273829439</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-68.53295684588105</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-41.22061600089502</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-15.49177601499922</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>7.026007904140203</v>
@@ -2572,31 +2376,31 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.065555</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.074777</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.004076</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.009860000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.003358</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.001376</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.00048</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.001188</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.003721</v>
       </c>
     </row>
     <row r="41">
@@ -2621,31 +2425,31 @@
         <v>2.437729</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.145255</v>
+        <v>1.21081</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.678876</v>
+        <v>1.753653</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>4.175086</v>
+        <v>4.179162</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>7.92078</v>
+        <v>7.93064</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3.30735</v>
+        <v>3.310708</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>8.629697</v>
+        <v>8.631073000000001</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>6.143864</v>
+        <v>6.144344</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>8.357502999999999</v>
+        <v>8.358691</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>7.960133</v>
+        <v>7.963854</v>
       </c>
     </row>
     <row r="42">
@@ -2964,31 +2768,31 @@
         <v>0.166325</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.195224</v>
+        <v>0.129669</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.558902</v>
+        <v>0.484125</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.404318</v>
+        <v>0.400242</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.061884</v>
+        <v>0.058526</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.364402</v>
+        <v>0.363026</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.537457</v>
+        <v>0.536977</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.459425</v>
+        <v>0.458237</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.067708</v>
+        <v>1.063987</v>
       </c>
     </row>
     <row r="49">
@@ -3908,7 +3712,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.613309</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0.698155</v>
@@ -3957,7 +3761,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.613309</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.698155</v>
@@ -5490,7 +5294,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-2.631462</v>
+        <v>0.131365</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-2.631462</v>
@@ -5502,7 +5306,7 @@
         <v>-0.9207959999999999</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.331759</v>
+        <v>0.695566</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.331759</v>
@@ -5517,7 +5321,7 @@
         <v>3.579224</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>3.579224</v>
+        <v>-0.999227</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>1.875185</v>
@@ -5686,46 +5490,46 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.013172</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.009646999999999999</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.089308</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.141329</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.184875</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.038889</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.160099</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.142235</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.057994</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.102919</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.097632</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.073785</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.005894</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-0.613262</v>
       </c>
     </row>
     <row r="104">
@@ -5833,46 +5637,46 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.449571</v>
+        <v>-0.436399</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.200402</v>
+        <v>0.190755</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.194206</v>
+        <v>-0.283514</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.42255</v>
+        <v>-0.563879</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-1.158551</v>
+        <v>-0.973676</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1.004932</v>
+        <v>1.043821</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.302159</v>
+        <v>-0.462258</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-2.352904</v>
+        <v>-2.210669</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-4.683528</v>
+        <v>-4.741522</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>2.85726</v>
+        <v>2.754341</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>3.740394</v>
+        <v>3.642762</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>3.392887</v>
+        <v>3.319102</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-1.107866</v>
+        <v>-1.11376</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.348078</v>
+        <v>-0.265184</v>
       </c>
     </row>
     <row r="107">
@@ -7335,7 +7139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R472"/>
+  <dimension ref="A1:R495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15556,7 +15360,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -16116,7 +15924,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -16422,7 +16234,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -17120,7 +16936,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -18392,7 +18212,11 @@
           <t>Net income (loss) - - - -</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -22764,7 +22588,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -27428,7 +27256,11 @@
           <t>Decrease (Increase) in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -29036,7 +28868,11 @@
           <t>Private placement (note 14(b)) 21,280,000 4,256,000</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -29814,7 +29650,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n">
         <v>0.131365</v>
       </c>
@@ -32034,7 +31874,11 @@
           <t>Increase in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -32548,7 +32392,11 @@
           <t>Proceeds from private placement (note 13)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -37210,7 +37058,11 @@
           <t>Decrease (Increase) in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E355" s="5" t="n">
         <v>0.013172</v>
       </c>
@@ -40069,25 +39921,17 @@
           <t>TotalRevenue</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E388" s="5" t="n">
+        <v>5.152251</v>
+      </c>
+      <c r="F388" s="5" t="n">
+        <v>3.839703</v>
+      </c>
+      <c r="G388" s="5" t="n">
+        <v>4.040124</v>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>5.943773</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -40139,25 +39983,17 @@
           <t>CostOfRevenue</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E389" s="5" t="n">
+        <v>2.50503</v>
+      </c>
+      <c r="F389" s="5" t="n">
+        <v>2.882018</v>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>2.493737</v>
+      </c>
+      <c r="H389" s="5" t="n">
+        <v>3.250899</v>
       </c>
       <c r="I389" s="5" t="n">
         <v>4.848332</v>
@@ -40207,25 +40043,17 @@
           <t>GrossProfit</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E390" s="5" t="n">
+        <v>2.647221</v>
+      </c>
+      <c r="F390" s="5" t="n">
+        <v>0.957685</v>
+      </c>
+      <c r="G390" s="5" t="n">
+        <v>1.546387</v>
+      </c>
+      <c r="H390" s="5" t="n">
+        <v>2.692874</v>
       </c>
       <c r="I390" s="5" t="n">
         <v>5.051543</v>
@@ -40537,25 +40365,17 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E394" s="5" t="n">
+        <v>2.210581</v>
+      </c>
+      <c r="F394" s="5" t="n">
+        <v>2.930544</v>
+      </c>
+      <c r="G394" s="5" t="n">
+        <v>3.242825</v>
+      </c>
+      <c r="H394" s="5" t="n">
+        <v>3.740182</v>
       </c>
       <c r="I394" s="5" t="n">
         <v>4.243305</v>
@@ -40703,10 +40523,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G396" s="5" t="n">
+        <v>0.001887</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -40765,15 +40583,11 @@
           <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E397" s="5" t="n">
+        <v>-0.047487</v>
+      </c>
+      <c r="F397" s="5" t="n">
+        <v>0.023246</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -43659,15 +43473,11 @@
           <t>OperatingIncome</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E432" s="5" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="F432" s="5" t="n">
+        <v>-1.492321</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -45212,7 +45022,11 @@
           <t>Income tax recovery (expense) (note 19)</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -45650,20 +45464,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F455" s="5" t="n">
+        <v>-1.97286</v>
+      </c>
+      <c r="G455" s="5" t="n">
+        <v>-1.696438</v>
+      </c>
+      <c r="H455" s="5" t="n">
+        <v>-1.047308</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
@@ -46767,25 +46575,17 @@
           <t>SellingAndMarketingExpense</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E468" s="5" t="n">
+        <v>0.725857</v>
+      </c>
+      <c r="F468" s="5" t="n">
+        <v>1.117211</v>
+      </c>
+      <c r="G468" s="5" t="n">
+        <v>1.237131</v>
+      </c>
+      <c r="H468" s="5" t="n">
+        <v>1.509004</v>
       </c>
       <c r="I468" s="5" t="n">
         <v>1.66254</v>
@@ -46855,25 +46655,17 @@
           <t>ResearchAndDevelopment</t>
         </is>
       </c>
-      <c r="E469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E469" s="5" t="n">
+        <v>0.254801</v>
+      </c>
+      <c r="F469" s="5" t="n">
+        <v>0.495488</v>
+      </c>
+      <c r="G469" s="5" t="n">
+        <v>0.447885</v>
+      </c>
+      <c r="H469" s="5" t="n">
+        <v>0.635325</v>
       </c>
       <c r="I469" s="5" t="n">
         <v>0.837369</v>
@@ -47181,6 +46973,2006 @@
         </is>
       </c>
       <c r="R472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>General and administrative (note 16)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="n">
+        <v>1.557809</v>
+      </c>
+      <c r="H473" s="5" t="n">
+        <v>1.595853</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G474" s="5" t="n">
+        <v>0.001887</v>
+      </c>
+      <c r="H474" s="5" t="n">
+        <v>0.000666</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G475" s="5" t="n">
+        <v>0.029187</v>
+      </c>
+      <c r="H475" s="5" t="n">
+        <v>0.125846</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Loss Before Taxes</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G476" s="5" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="H476" s="5" t="n">
+        <v>-0.9207959999999999</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Income Tax Expense (Recovery) (note Error! Reference source not found.)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G478" s="5" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="H478" s="5" t="n">
+        <v>-0.9207959999999999</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Basic and Diluted Loss Per Share (note 18) $</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G479" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H479" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding (note 18)</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G480" s="5" t="n">
+        <v>36.477196</v>
+      </c>
+      <c r="H480" s="5" t="n">
+        <v>49.488193</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>General and administrative (note 19)</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="n">
+        <v>1.317845</v>
+      </c>
+      <c r="G481" s="5" t="n">
+        <v>1.557809</v>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F482" s="5" t="n">
+        <v>0.023246</v>
+      </c>
+      <c r="G482" s="5" t="n">
+        <v>0.029187</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Gain on disposal of property, plant and equipment (note 13)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="n">
+        <v>0.00119</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Listing expense (note 7)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="n">
+        <v>-0.683038</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Loss Before Taxes</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="G485" s="5" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Income Tax Expense (Recovery) (note 20)</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="G487" s="5" t="n">
+        <v>-1.665364</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding (note 21)</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F488" s="5" t="n">
+        <v>22.654507</v>
+      </c>
+      <c r="G488" s="5" t="n">
+        <v>36.477196</v>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>General and administrative (see note 17)</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" s="5" t="n">
+        <v>1.229923</v>
+      </c>
+      <c r="F489" s="5" t="n">
+        <v>1.317845</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Gain on disposal of property, plant and equipment (see note 10)</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" s="5" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="F490" s="5" t="n">
+        <v>0.00119</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Write-down of inventory (see note 9)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" s="5" t="n">
+        <v>-0.07986799999999999</v>
+      </c>
+      <c r="F491" s="5" t="n">
+        <v>-0.480539</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Provision for inventory purchase order commitment (see note 12)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" s="5" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Listing expense (see note 6)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="n">
+        <v>-0.683038</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Income (Loss) Before Taxes</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E494" s="5" t="n">
+        <v>0.131365</v>
+      </c>
+      <c r="F494" s="5" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Net Income (Loss) and Comprehensive Income (Loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="n">
+        <v>0.131365</v>
+      </c>
+      <c r="F495" s="5" t="n">
+        <v>-2.631462</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
         <is>
           <t>-</t>
         </is>
